--- a/artfynd/A 59972-2025 artfynd.xlsx
+++ b/artfynd/A 59972-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173073</v>
       </c>
       <c r="B2" t="n">
-        <v>80048</v>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129173071</v>
+        <v>129173072</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428307</v>
+        <v>428348</v>
       </c>
       <c r="R3" t="n">
-        <v>6682849</v>
+        <v>6682810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129173072</v>
+        <v>129173071</v>
       </c>
       <c r="B4" t="n">
-        <v>80175</v>
+        <v>80392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428348</v>
+        <v>428307</v>
       </c>
       <c r="R4" t="n">
-        <v>6682810</v>
+        <v>6682849</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 59972-2025 artfynd.xlsx
+++ b/artfynd/A 59972-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173073</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173072</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>